--- a/artfynd/A 37115-2021 artfynd.xlsx
+++ b/artfynd/A 37115-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37115-2021 artfynd.xlsx
+++ b/artfynd/A 37115-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,6 +804,230 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132607303</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80982</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>1,5 km N om Ämneboda, Bl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>487075</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6238875</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlshamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Asarum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1996-04-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1996-04-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>spridd på många träd</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>bäckkärr med al, ask och gran</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>klibbal, gran</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132607305</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1036</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Hållav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Menegazzia terebrata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>1,5 km N om Ämneboda, Bl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>487075</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6238875</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlshamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Asarum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1996-04-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1996-04-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på 3 klibbalar</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>bäckkärr med al, ask och gran</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37115-2021 artfynd.xlsx
+++ b/artfynd/A 37115-2021 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>132607303</v>
       </c>
       <c r="B3" t="n">
-        <v>80982</v>
+        <v>80984</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>132607305</v>
       </c>
       <c r="B4" t="n">
-        <v>79432</v>
+        <v>79434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37115-2021 artfynd.xlsx
+++ b/artfynd/A 37115-2021 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>132607303</v>
       </c>
       <c r="B3" t="n">
-        <v>80984</v>
+        <v>80992</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>132607305</v>
       </c>
       <c r="B4" t="n">
-        <v>79434</v>
+        <v>79442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37115-2021 artfynd.xlsx
+++ b/artfynd/A 37115-2021 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>132607303</v>
       </c>
       <c r="B3" t="n">
-        <v>80992</v>
+        <v>80993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>132607305</v>
       </c>
       <c r="B4" t="n">
-        <v>79442</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37115-2021 artfynd.xlsx
+++ b/artfynd/A 37115-2021 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>132607303</v>
       </c>
       <c r="B3" t="n">
-        <v>80993</v>
+        <v>80994</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>132607305</v>
       </c>
       <c r="B4" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37115-2021 artfynd.xlsx
+++ b/artfynd/A 37115-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>108100359</v>
       </c>
       <c r="B2" t="n">
-        <v>78001</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487075.2189366779</v>
+        <v>487075</v>
       </c>
       <c r="R2" t="n">
-        <v>6238874.773749334</v>
+        <v>6238875</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1996-04-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1996-04-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132607303</v>
+        <v>132607305</v>
       </c>
       <c r="B3" t="n">
-        <v>80998</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230185</v>
+        <v>1036</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -882,7 +867,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>spridd på många träd</t>
+          <t>på 3 klibbalar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +886,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>klibbal, gran</t>
+          <t>klibbal</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,32 +904,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132607305</v>
+        <v>132607303</v>
       </c>
       <c r="B4" t="n">
-        <v>79448</v>
+        <v>81036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1036</v>
+        <v>230185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hållav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Menegazzia terebrata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -994,7 +979,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på 3 klibbalar</t>
+          <t>spridd på många träd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +998,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>klibbal</t>
+          <t>klibbal, gran</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
